--- a/human_resources_surveys/012_meeting_psychological_safety_survey--human_resources_surveys.xlsx
+++ b/human_resources_surveys/012_meeting_psychological_safety_survey--human_resources_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>very_good</t>
+          <t>very good</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>very_likely</t>
+          <t>very likely</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>somewhat_likely</t>
+          <t>somewhat likely</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>not_likely</t>
+          <t>not likely</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1297,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>not_at_all_likely</t>
+          <t>not at all likely</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>very_safe</t>
+          <t>very safe</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1331,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>somewhat_safe</t>
+          <t>somewhat safe</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>not_safe</t>
+          <t>not safe</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>not_at_all_safe</t>
+          <t>not at all safe</t>
         </is>
       </c>
     </row>
@@ -1399,7 +1399,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>most_of_the_time</t>
+          <t>most of the time</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>some_of_the_time</t>
+          <t>some of the time</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>strongly_agree</t>
+          <t>strongly agree</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>somewhat_agree</t>
+          <t>somewhat agree</t>
         </is>
       </c>
     </row>
@@ -1603,7 +1603,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>somewhat_disagree</t>
+          <t>somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>strongly_disagree</t>
+          <t>strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>most_of_the_time</t>
+          <t>most of the time</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>some_of_the_time</t>
+          <t>some of the time</t>
         </is>
       </c>
     </row>
@@ -1722,7 +1722,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>very_satisfied</t>
+          <t>very satisfied</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>very_dissatisfied</t>
+          <t>very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1824,7 +1824,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>most_of_the_time</t>
+          <t>most of the time</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1841,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>some_of_the_time</t>
+          <t>some of the time</t>
         </is>
       </c>
     </row>
@@ -1892,7 +1892,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>strongly_agree</t>
+          <t>strongly agree</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>somewhat_agree</t>
+          <t>somewhat agree</t>
         </is>
       </c>
     </row>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>somewhat_disagree</t>
+          <t>somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>strongly_disagree</t>
+          <t>strongly disagree</t>
         </is>
       </c>
     </row>
